--- a/SGC-CKN/Excel/5b214dd5-f1a1-447e-b48e-766b23fe8bd1_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-28_D800_16-03-2026.xlsx
+++ b/SGC-CKN/Excel/5b214dd5-f1a1-447e-b48e-766b23fe8bd1_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-28_D800_16-03-2026.xlsx
@@ -17,7 +17,7 @@
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P11-28</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t/>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>SGC-KCN0003</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Đất lấp</t>
+    <t>Đất san lấp / Cát san lấp</t>
   </si>
   <si>
     <t xml:space="preserve">08:10
@@ -106,10 +106,13 @@
 16/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">08:20
@@ -119,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">09:00
@@ -133,7 +136,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét- đồi chỗ kép cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">12:00
@@ -153,9 +156,6 @@
     <t>6</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
-  </si>
-  <si>
     <t xml:space="preserve">13:00
 16/03/2026</t>
   </si>
@@ -167,7 +167,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">16:25
@@ -177,7 +177,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">16:05
@@ -194,7 +194,7 @@
     <t>9</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">18:53
@@ -1201,21 +1201,21 @@
         <v>6.68</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>29</v>
@@ -1236,24 +1236,24 @@
         <v>19.92</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F13" s="12">
         <v>-3.33</v>
@@ -1271,24 +1271,24 @@
         <v>10.2</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="15">
         <v>-13.53</v>
@@ -1306,24 +1306,24 @@
         <v>2.6</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F15" s="19">
         <v>-18.73</v>
@@ -1341,18 +1341,18 @@
         <v>6.42</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D16" s="24" t="s">
         <v>45</v>
@@ -1376,7 +1376,7 @@
         <v>2.91</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1411,7 +1411,7 @@
         <v>2.31</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1481,7 +1481,7 @@
         <v>2.08</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1656,7 +1656,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1685,7 +1685,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1714,7 +1714,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1743,7 +1743,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1885,10 +1885,10 @@
         <v>67</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D11" s="36">
         <v>9</v>
